--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_001/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_001/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -565,6 +570,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -600,6 +620,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -675,6 +700,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -710,11 +740,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -761,46 +786,6 @@
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1448,12 +1433,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Predict blood temperature rise and housing surface temperature for implantable LVAD motor thermal safety assessment</t>
+          <t>Predict blood temperature rise and housing surface temperature for LVAD motor thermal safety assessment</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>A conjugate heat transfer CFD model (Ansys Fluent 2024R1) predicts peak wetted-wall temperature, average housing outer surface temperature, bulk blood outlet temperature rise, and heat split to blood for a brushless DC LVAD motor. The model is used to demonstrate that blood temperature rise remains ≤2.0 C and housing external surfaces remain ≤41 C under worst foreseeable use (2–6 L/min, 6,000–9,000 rpm, 2.6–3.4 W motor loss) for adult patients (55–100 kg). Results support design-freeze sign-off and regulatory submission for thermal safety.</t>
+          <t>A conjugate heat transfer CFD model (Ansys Fluent 2024R1) of a brushless DC LVAD motor predicts bulk outlet blood temperature rise and peak housing surface temperature across 2–6 L/min and 6,000–9,000 rpm. Results support design sign-off and regulatory submission for thermal safety, requiring blood temperature rise ≤2.0 C and exterior housing ≤41 C under worst foreseeable use.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1483,7 +1468,7 @@
       </c>
       <c r="I3" s="39" t="inlineStr">
         <is>
-          <t>Thermal-Fluid Modeling Group, CardioMech Devices Inc. (Analysis lead: S. Kim, PhD)</t>
+          <t>Thermal-Fluid Modeling Group, CardioMech Devices Inc.</t>
         </is>
       </c>
       <c r="J3" s="22" t="inlineStr">
@@ -1491,9 +1476,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md — Credibility Assessment Report, Conjugate Heat Transfer Model of an Implantable LVAD Motor, Rev R1.3, 2026-08-06, CardioMech Devices Inc.</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2089,7 +2074,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Thermal Safety Performance Requirements</t>
+          <t>Thermal Safety Performance Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2099,7 +2084,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Blood temperature rise ≤2.0 C and housing external surface temperature ≤41 C under worst foreseeable use; model prediction error ≤0.2 C mean bias and ≤0.3 C 95% limit for outlet ΔT; ≤0.7 C 95% uncertainty for peak housing surface temperature; numerical error &lt;5% of total energy input and &lt;0.1 C on temperature metrics</t>
+          <t>Blood temperature rise must remain ≤2.0 C and housing external surface temperature ≤41 C under worst foreseeable use across the intended operating envelope (2–6 L/min, 6,000–9,000 rpm, 2.6–3.4 W motor loss); model prediction error must be ≤0.2 C mean bias and ≤0.3 C 95% limit for outlet temperature rise, and ≤0.7 C 95% uncertainty for peak housing surface temperature.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2127,7 +2112,7 @@
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer model with SST k-ω turbulence, Bird-Carreau blood rheology, frozen rotor frame, and volumetric heat sources; M2 mesh (12.8M cells) used for all production cases; Monte Carlo UQ with 300 LHS samples per operating condition</t>
+          <t>Steady-state conjugate heat transfer model with incompressible shear-thinning blood analog (Bird-Carreau), SST k-ω turbulence, rotating reference frame, and volumetric heat sources representing motor copper and iron losses in titanium/epoxy/aluminum assembly.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2141,13 +2126,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Mock Circulatory Loop Thermal Validation Dataset</t>
+          <t>Mock Circulatory Rig Thermal Test Data</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Eight operating-point thermal measurements (outlet ΔT, housing surface temperature, IR thermograms) from production-equivalent LVAD SN M-THERM-017 in glycerol-saline blood analog at 37 C, with NIST-traceable instrumentation calibrated to WI-THERM-07</t>
+          <t>Eight operating-point measurements of outlet blood temperature rise, housing surface temperature (IR + PT100), and electrical input power from production-equivalent LVAD (SN M-THERM-017) in glycerol-saline blood analog at 37 C using NIST-traceable instrumentation.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2161,23 +2146,35 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Motor Electrical Loss Characterization Dataset</t>
+          <t>Motor Electrical Loss Calibration Data</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Measured copper and iron losses vs rpm and torque used to calibrate volumetric heat generation inputs; power analyzer accuracy ±0.05% FS; Normal(3.0 W, 0.2 W) distribution characterised for UQ propagation</t>
+          <t>Bench dynamometer power measurements with calibrated Yokogawa WT5000 analyzer (±0.05% FS) providing Normal(3.0 W, 0.2 W) distributions for motor loss input uncertainty propagation across rpm/torque duty points.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Material and Fluid Property Data</t>
+        </is>
+      </c>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Blood analog and structural material thermal properties (ρ, μ(γ̇), k, cp for blood; k for Ti Grade 5, epoxy potting, aluminum saddle) with uncertainty distributions for Monte Carlo propagation; thermal contact conductance bounds from clamp torque tolerance and grease coverage inspection.</t>
+        </is>
+      </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -2317,7 +2314,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Analytical and Benchmark Code Verification</t>
+          <t>Outlet Blood Temperature Rise Model-to-Test Comparison</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2332,27 +2329,27 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Fluent 2024R1 results compared against closed-form composite slab conduction with internal heat generation (10 cases), Gnielinski correlation for forced convection in heated pipe (Re 10,000–50,000), and NASA conjugate cylinder crossflow case (Re=4,000). Vendor thermal regression suite (18 heat-transfer cases) executed and passed.</t>
+          <t>Model-predicted bulk outlet temperature rise (ΔTout) compared to fiber-optic probe measurements at 8 operating points (2–6 L/min, 7,000–9,000 rpm, 2.6–3.4 W) in production-equivalent LVAD on mock circulatory rig with glycerol-saline blood analog.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Analytical solutions, Gnielinski correlation, NASA LES published reference, Fluent 2024R1 vendor regression suite (QA-FLU-REG-2024R1-TH)</t>
+          <t>Neoptix T1 fiber optic probe measurements (±0.1 C, NIST-traceable), repeatability ±0.05 C</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>Quantitative result if applicable</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Combined Type A and B uncertainty budget; Monte Carlo with 300 LHS samples; additive model discrepancy Gaussian with σ = RMSE of residuals</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Composite slab: ≤0.05 C absolute; Gnielinski Nu: 2.3% deviation; NASA cylinder Nu: 3.1% deviation; regression suite: 18/18 pass</t>
+          <t>Mean absolute deviation 0.08 C; maximum deviation 0.19 C (at 2 L/min, 9,000 rpm); 7/8 points within 1σ_meas; 1/8 point at 1.6σ_meas; combined measurement uncertainty ±0.12 C (k=2)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2364,7 +2361,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence and GCI Study</t>
+          <t>Peak Housing Surface Temperature Model-to-Test Comparison</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2375,12 +2372,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Three meshes (M1 6.2M, M2 12.8M, M3 24.6M cells) evaluated at 4 L/min, 8,000 rpm, 3.0 W. Richardson extrapolation and GCI95 computed for peak wall temperature, bulk outlet ΔT, and heat split. Transient check with moving reference frame confirmed steady RRF approximation valid.</t>
+          <t>Model-predicted peak housing exterior surface temperature compared to FLIR A655sc IR thermography (full-field) and PT100 contact sensors at 8 operating points; hot-spot location and magnitude assessed.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolated values; steady vs transient cycle-averaged temperatures</t>
+          <t>FLIR A655sc IR camera (emissivity-calibrated on Ti) cross-checked with bonded PT100s (±0.1 C); surface mapping uncertainty ±0.2 C</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2390,12 +2387,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation; Grid Convergence Index (GCI95)</t>
+          <t>Monte Carlo UQ with additive model discrepancy; IR vs PT100 cross-check</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Peak wall temp GCI95 on M2: 0.04 C (0.1%); outlet ΔT GCI95: 0.01 C; heat split GCI95: 0.3%; energy balance closure: 0.3%; transient vs steady difference: 0.03 C</t>
+          <t>Mean absolute deviation 0.31 C; maximum deviation 0.48 C (at 6 L/min, 9,000 rpm); all 8 points within 2σ_meas; hot-spot location reproduced within 6 mm</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2407,7 +2404,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Monitoring</t>
+          <t>Mesh Convergence and GCI Study</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2418,23 +2415,27 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Nonlinear residuals monitored for all production M2 runs; energy, momentum, and turbulence residual targets enforced. Global energy balance checked across all cases.</t>
+          <t>Three systematically refined meshes (M1: 6.2M, M2: 12.8M, M3: 24.6M cells) evaluated at 4 L/min, 8,000 rpm, 3.0 W for peak wall temperature, outlet ΔT, and heat split to blood using Richardson extrapolation and GCI95.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Prescribed residual targets; global energy balance</t>
+          <t>Richardson extrapolated value; GCI95 thresholds (&lt;5% numerical error, &lt;0.1 C on temperature metrics)</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Richardson extrapolation; Grid Convergence Index (GCI95)</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Energy residual &lt;1e-6; momentum and turbulence &lt;1e-5; global energy balance within 0.3%</t>
+          <t>Peak wall temperature GCI95 on M2 = 0.04 C (0.1% absolute); outlet ΔT GCI95 = 0.01 C; heat split GCI95 = 0.3%; observed order 1.98; global energy balance closed within 0.3%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2446,7 +2447,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Model-to-Test Comparison — Outlet Blood Temperature Rise</t>
+          <t>Analytical Benchmark and Code Verification</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2457,27 +2458,23 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Predicted bulk outlet ΔTout compared against fiber-optic probe measurements at 8 operating points spanning 2–6 L/min and 2.6–3.4 W motor loss. No free parameter tuning; boundary conditions set to match measured electrical loss.</t>
+          <t>Fluent 2024R1 verified against closed-form composite slab conduction (10 cases), Gnielinski Nusselt correlation for heated pipe (Re 10,000–50,000), and NASA conjugate cylinder HTC benchmark (Re=4,000, Pr=0.7). Vendor thermal regression suite (18 cases) also executed.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Neoptix T1 fiber optic probe measurements (±0.1 C, NIST-traceable); experimental uncertainty ±0.12 C (k=2)</t>
+          <t>Closed-form analytical solutions; Gnielinski correlation; NASA/LES published reference; Fluent vendor regression suite QA-FLU-REG-2024R1-TH</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Combined Type A and B uncertainty budget; error normalized by measurement uncertainty (sigma units)</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Mean absolute deviation 0.08 C; maximum deviation 0.19 C (at 2 L/min, 9,000 rpm); 7/8 points |error|&lt;1σ_meas; 1/8 point 1.6σ</t>
+          <t>Conduction benchmark: within 0.05 C absolute; Nusselt number pipe: within 2.3%; NASA cylinder Nu: within 3.1% of LES reference; all 18 vendor regression cases passed</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2489,7 +2486,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Model-to-Test Comparison — Peak Housing Surface Temperature</t>
+          <t>Monte Carlo Uncertainty Propagation and Margin Assessment</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2500,12 +2497,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Predicted housing surface temperatures compared to FLIR IR thermography and PT100 bonded sensors at 8 operating points. Spatial hot-spot location also compared to IR maps.</t>
+          <t>300 Latin Hypercube samples per operating condition propagated through M2 model incorporating input uncertainty distributions (motor loss, contact conductance, blood k, blood cp, flow rate) and numerical error injection (GCI/2 additive noise). Model discrepancy added as Gaussian with σ = RMSE of validation residuals. Results compared to safety thresholds.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>FLIR A655sc IR camera (emissivity-calibrated) and PT100 sensors (±0.1 C); surface temperature mapping uncertainty ±0.2 C</t>
+          <t>Safety thresholds: blood ΔT ≤2.0 C; housing surface ≤41 C</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2515,12 +2512,12 @@
       </c>
       <c r="G7" s="41" t="inlineStr">
         <is>
-          <t>Combined measurement uncertainty; error normalized by measurement uncertainty</t>
+          <t>Monte Carlo with Latin Hypercube Sampling; Sobol sensitivity indices via polynomial chaos surrogate (R²=0.995); Morris screening; additive model discrepancy</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Mean absolute deviation 0.31 C; maximum 0.48 C (at 6 L/min, 9,000 rpm); all 8 points within 2σ_meas; hot-spot location within 6 mm</t>
+          <t>95% upper bound ΔTout at 2 L/min 3.4 W loss = 1.35 C (threshold 2.0 C); peak surface 95% upper bound ≤40.8 C (threshold 41 C); all scenarios below thresholds</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2530,47 +2527,14 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="41" t="inlineStr">
-        <is>
-          <t>Monte Carlo Uncertainty Propagation and Decision-Space Bounds</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
       <c r="C8" s="33" t="n"/>
-      <c r="D8" s="41" t="inlineStr">
-        <is>
-          <t>300 LHS Monte Carlo samples per operating condition propagated through M2 model with input distributions from Section 5. Numerical error injected as additive Gaussian (σ=GCI/2). Model discrepancy from validation residuals added. 95% prediction bounds compared to safety thresholds.</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>Safety thresholds: ΔTout ≤2.0 C; surface temperature ≤41 C</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="41" t="inlineStr">
-        <is>
-          <t>Latin Hypercube Sampling Monte Carlo; Sobol sensitivity indices via polynomial chaos surrogate (R²=0.995); additive model discrepancy</t>
-        </is>
-      </c>
-      <c r="H8" s="41" t="inlineStr">
-        <is>
-          <t>95% upper bound ΔTout at 2 L/min, 3.4 W: 1.35 C (threshold 2.0 C); 95% upper bound surface temp: ≤40.8 C (threshold 41 C); all scenarios below thresholds with margin</t>
-        </is>
-      </c>
-      <c r="I8" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="24" t="n"/>
@@ -2777,12 +2741,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with regression testing, version control, and quality management documentation</t>
+          <t>Commercial solver with demonstrated QA processes; regression testing on heat-transfer cases; version control of all case files and scripts</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2024R1 used with vendor thermal regression suite (18 heat-transfer cases, all passed; report QA-FLU-REG-2024R1-TH). All solver scripts and case files tracked in Git (repo LVAD-CHT, tag v1.3.2) with immutable SHA digests in run log RL-CHT-017. Work governed by SOP-MOD-007. Files stored in validated PLM system (SIM-THERM-LVAD-R1.3) with access control and audit trail. Fluent journal files ensure button-for-button repeatability. Platform reproducibility verified across Xeon and AMD EPYC nodes (difference &lt;0.01 C on same platform; &lt;0.06 C cross-platform attributable to closure differences).</t>
+          <t>Ansys Fluent 2024R1 used under version control (Git repo LVAD-CHT, tag v1.3.2). Vendor thermal regression suite executed with all 18 heat-transfer cases passing (QA-FLU-REG-2024R1-TH). Case files, meshes, and post-processing scripts tracked with immutable SHA digests (RL-CHT-017). Work follows SOP-MOD-007 (Simulation Controls and Records) with PLM storage, access control, and audit trail under item SIM-THERM-LVAD-R1.3. Determinism confirmed: reruns on same platform reproduced within 0.01 C.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2810,12 +2774,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations; benchmarked against analytical solutions and published references</t>
+          <t>Comparison to analytical solutions and published benchmarks for conjugate heat transfer physics; agreement within accepted engineering tolerances</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Three independent benchmark comparisons performed: (1) composite slab conduction with internal heat generation — Fluent within 0.05 C absolute across 10 cases; (2) Gnielinski forced convection correlation in heated pipe at Re=10,000–50,000 — 2.3% Nu deviation; (3) NASA conjugate cylinder crossflow (Re=4,000, Pr=0.7) — surface-averaged Nu within 3.1% of published LES reference. All 18 vendor heat-transfer regression cases passed. These checks specifically exercise the conjugate coupling and wall flux exchange relevant to the LVAD application.</t>
+          <t>Three independent code-level verifications performed: (1) composite slab conduction with internal heat generation — Fluent within 0.05 C of closed-form across 10 cases; (2) Gnielinski forced convection in heated pipe — Nusselt within 2.3% for Re 10,000–50,000 using same wall treatment and SST model; (3) NASA conjugate cylinder benchmark at Re=4,000 — surface-averaged Nu within 3.1% of published LES reference, validating fluid-solid coupling and wall flux exchange.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2843,12 +2807,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with GCI &lt;5% of total energy input and &lt;0.1 C on temperature metrics</t>
+          <t>Mesh convergence demonstrated; GCI below 5% of electrical loss contribution; temperature discretization error below 0.1 C</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh convergence study (M1 6.2M, M2 12.8M, M3 24.6M cells) with Richardson extrapolation and GCI95 computed for all key QoIs. Peak wall temperature GCI95=0.04 C (0.1% of absolute); outlet ΔT GCI95=0.01 C; heat split GCI95=0.3% — all well below the 0.1 C numerical error requirement. Observed order 1.98 consistent with second-order scheme. Transient moving-reference-frame check confirmed steady RRF approximation introduces only 0.03 C difference in cycle-averaged temperatures. GCI numerical uncertainty was injected as additive Gaussian noise in Monte Carlo propagation, providing full traceability to decision bounds.</t>
+          <t>Three systematically refined meshes (M1: 6.2M, M2: 12.8M, M3: 24.6M cells) with controlled prism layer refinement. Richardson extrapolation with observed order 1.98 (near theoretical for second-order scheme). GCI95 on production mesh M2: peak wall temperature 0.04 C (0.1% absolute), outlet ΔT 0.01 C, heat split 0.3% — all well below stated thresholds. Global energy balance closed within 0.3% across all cases. Transient check confirmed steady RRF approximation valid: cycle-averaged temperatures within 0.03 C. Numerical error injected as additive noise in Monte Carlo for conservative propagation.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2869,19 +2833,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residuals reduced to specified targets; global energy balance closure demonstrated</t>
+          <t>Residuals reduced to levels demonstrating iterative convergence; global energy balance verified</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>All production M2 runs converged to energy residuals below 1e-6 and momentum/turbulence residuals below 1e-5. Global energy balance (electrical loss minus enthalpy rise plus solid conduction to saddle) closed within 0.3% across all cases. Pseudo-transient CFL~50 acceleration documented in solver settings (Appendix A2). Residual histories available in figs/residuals/ for all runs.</t>
+          <t>Nonlinear residuals reduced below 1e-6 for energy equation and 1e-5 for momentum and turbulence across all M2 production cases. Global energy balance (electrical loss minus sum of enthalpy rise and solid conduction to saddle) closed within 0.3% for all runs. Pseudo-transient acceleration (CFL ~50) used with relaxation factors documented (pressure 0.3, momentum 0.7, energy 1.0). Residual histories available in run log (figs/residuals/). Reproducibility on same platform confirmed within 0.01 C.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2909,12 +2873,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Model set-up independently reviewed; boundary conditions verified against test conditions; mesh quality documented</t>
+          <t>Independent review of model setup, boundary conditions, and post-processing; traceability of case files to test conditions</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Independent internal peer review conducted by Structures &amp; Reliability group (IRR-CHT-2026-04). External SME review by Prof. M. Hart (Univ. of Michigan) on turbulence and HTC treatment, with feedback incorporated in Section 8. Assumption log AL-CHT-2026-03 documents rationale for neglected radiation and SST selection. CCN-THERM-71 documents mesh upgrade impact. Boundary conditions set directly from measured electrical loss at each operating point with no free tuning. All case files have immutable SHA digests and are reproducible from documented journals.</t>
+          <t>Independent internal peer review performed by Structures &amp; Reliability group (IRR-CHT-2026-04). External SME review by Prof. M. Hart (Univ. of Michigan) on turbulence and HTC treatment with feedback incorporated. Boundary conditions aligned to measured electrical loss at each test point with no free parameter tuning (contact conductance held at midrange). Assumption log AL-CHT-2026-03 records rationale for neglected effects. Change control entry CCN-THERM-71 documents mesh upgrade with impact statement. All 8 simulation-to-test case mappings explicitly documented in Table A1.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2942,12 +2906,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equation and turbulence model selection justified; key physics included; alternatives evaluated; known limitations documented</t>
+          <t>Governing equation choices justified; turbulence model selection supported by comparison with alternatives; documented known limitations</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive choices comprehensively justified: SST k-ω selected over realizable k-ε with quantified comparison (+0.06 C wall temp, +0.03 C ΔTout difference favoring SST); Bird-Carreau shear-thinning retained over Newtonian due to up to 0.08 C difference at 2 L/min; radiation estimated &lt;0.01 W and neglected with documented rationale; frozen rotor vs transient sliding mesh compared (0.03 C difference). Known limitations documented: low-flow transitional regime, absence of hemolysis coupling, contact conductance inferred from process parameters, and near-wall RBC migration not modeled. Model form uncertainty folded into validation error rather than parametric uncertainty.</t>
+          <t>SST k-ω selected over realizable k-ε with quantified comparison: k-ε underpredicted HTC leading to +0.06 C wall temperature and +0.03 C ΔTout difference; validation data favored SST. Bird-Carreau shear-thinning rheology justified over Newtonian: Newtonian shifted ΔTout by up to 0.08 C at 2 L/min — significant given the 2 L/min operating floor. Radiative exchange quantified at &lt;0.01 W and justifiably neglected. Steady frozen-rotor vs transient sliding mesh checked: time-averaged ΔTout differed by 0.03 C. Assumption log AL-CHT-2026-03 records rationale. Limitations clearly documented (low-flow transitional regime, no hemolysis/protein denaturation coupling, tissue conduction outside saddle not modeled).</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2975,12 +2939,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties and boundary conditions from measurements with uncertainty characterization; input uncertainty propagated</t>
+          <t>Material properties from testing or calibrated sources; boundary conditions from measurements; input uncertainty characterized with distributions</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>All key inputs characterized with probability distributions: motor loss Normal(3.0 W, σ=0.2 W) from calibrated dynamometer (Yokogawa WT5000, ±0.05% FS); thermal contact conductance Triangular(6000, 10000, 15000 W/m²K) from process tolerance; blood k Normal(0.52, 0.02) W/m-K; blood cp Normal(3680, 120) J/kg-K; flow rate σ=1.5% from calibrated ultrasonic meter. Titanium, epoxy, and aluminum properties specified by grade/spec. Sobol first-order and total-order sensitivity indices computed for all inputs via polynomial chaos surrogate (R²=0.995). Limitations noted for contact conductance (process-inferred rather than directly measured on assembled joint) and extreme patient outliers.</t>
+          <t>Motor electrical loss characterized as Normal(3.0 W, 0.2 W) from bench dynamometer with calibrated Yokogawa WT5000 (±0.05% FS). Blood analog properties at 37 C specified with uncertainty distributions for cp Normal(3680, 120) J/kg-K and k Normal(0.52, 0.02) W/m-K reflecting patient variability. Thermal contact conductance as Triangular(6000, 10000, 15000) W/m²-K from process tolerance. Flow rate uncertainty Normal with σ=1.5% from NIST-traceable Transonic T201 (RMSE 0.7% of reading). All instrument calibrations traceable (CAL-NEO-2026-0415). Sobol sensitivity analysis identified dominant inputs. One noted gap: contact conductance distribution inferred from process parameters rather than direct measurement on assembled joint.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -3008,12 +2972,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Production-representative test articles with adequate characterization; statistical sample justification</t>
+          <t>Production-representative test article; adequate sample characterization; test repeatability demonstrated</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>One production-equivalent LVAD (SN M-THERM-017) tested with same housing, potting, and saddle geometry as final design Rev D. Saddle prepared per WI-THERM-07 (grease spec and torque). Eight operating points tested across the full flow and loss envelope. Two repeat runs at 4 L/min, 8,000 rpm demonstrated repeatability of ±0.05 C. Probe zero drift checked in ice bath (±0.03 C). However, only a single unit was tested; no statistical characterization across multiple production units or hematocrit-matched blood analogs at multiple viscosity batches. This is a moderate gap for a Class III device.</t>
+          <t>Single production-equivalent LVAD (SN M-THERM-017) used with same housing, potting, and saddle as final design Rev D, prepared per controlled work instruction WI-THERM-07. Eight distinct operating points tested. Repeatability demonstrated at 4 L/min, 8,000 rpm with two repeated runs showing ±0.05 C for outlet rise. However, only one physical device unit was tested; no inter-unit variability data provided. The fluid viscosity was tuned to match blood analog shear within Re and Pr within 10% of target. Limitation: single specimen reduces ability to characterize manufacturing variability effects on thermal performance.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -3041,12 +3005,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation with traceable uncertainty; controlled environmental conditions; measurement uncertainty budget documented</t>
+          <t>Calibrated instrumentation; NIST-traceable; controlled environment; measurement uncertainty quantified</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>All instruments NIST-traceable and recently calibrated: Neoptix T1 fiber optic probes (±0.1 C, cert CAL-NEO-2026-0415, 2026-04-15); Transonic T201 flow meter (±1.5%, RMSE 0.7% of reading); FLIR A655sc IR camera (emissivity calibrated, validated to PT100 within 0.12 C); Yokogawa WT5000 power analyzer (±0.05% FS). Thermal leakage to ambient quantified by calorimetry (0.08±0.03 W) and corrected. Steady-state achieved after 20 min stabilization; 5-min averaged data at 10 Hz. Combined Type A+B uncertainty budget for outlet ΔT: ±0.12 C (k=2); surface temperature: ±0.2 C. EMI immunity of fiber optic probes appropriate for motor environment.</t>
+          <t>All instruments NIST-traceable: Neoptix T1 fiber optic probes (±0.1 C, cert CAL-NEO-2026-0415), Transonic T201 flow meter (±1.5%, RMSE 0.7%), FLIR A655sc IR camera (emissivity calibrated on Ti, validated to PT100 ≤0.12 C), Yokogawa WT5000 (±0.05% FS). Probe zero drift verified ±0.03 C in ice bath. 20-minute stabilization before data capture; 5-minute averaging at 10 Hz after steady state. Thermal leakage to ambient quantified at 0.08±0.03 W and corrected. Fluid temperature controlled at 37.0±0.2 C. Combined outlet temperature rise uncertainty ±0.12 C (k=2); surface temperature ±0.2 C.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3074,12 +3038,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model boundary conditions set to match measured experimental conditions; no free parameter tuning for validation comparison</t>
+          <t>Model boundary conditions matched to measured test conditions at each point; no free-parameter tuning; uncertainty propagated</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Motor electrical loss boundary condition set directly to measured value at each of 8 operating points (no tuning). Contact conductance held at midrange 10,000 W/m²K (prior to any fitting exercise). A single-parameter sensitivity exercise showed best-fit conductance of 9,200 W/m²K reduced surface temperature bias by 0.07 C, but this value was not adopted for predictions — the midrange was retained and the spread treated as uncertainty. Reynolds numbers within 10% of in vivo target; Prandtl number of blood analog (21.4) within 3.4% of blood nominal (20.7). Heat generation placement mirrors real motor via distributed body source from winding layout. Simulation-to-test case mapping fully documented in Appendix A1 table.</t>
+          <t>Electrical loss boundary condition set to match measured value at each of 8 operating points (no free tuning). Contact conductance held at 10,000 W/m²-K midrange with sensitivity treated as uncertainty rather than calibration. Reynolds numbers within 10% of in vivo equivalents using viscosity-matched analog; Prandtl number 21.4 vs 20.7 nominal (negligible scaling impact documented). Heat generation placement mirrored real motor via distributed body sources from winding layout. Probe placement (10D upstream/downstream) confirmed non-intrusive to local HTC. Single-parameter adjustment exercise documented to avoid overfitting. All 8 simulation-to-test mappings explicitly recorded in Table A1.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3107,12 +3071,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative agreement within stated error bounds across multiple operating points; comparison normalized by measurement uncertainty</t>
+          <t>Quantitative error metrics across multiple operating points; comparison normalized to measurement uncertainty; spatial pattern validation; uncertainty bands overlap</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Outlet ΔTout: mean absolute deviation 0.08 C (target ≤0.2 C bias), maximum 0.19 C (target ≤0.3 C 95% limit); 7/8 points within 1σ_meas, 1/8 at 1.6σ. Peak housing surface temperature: mean absolute deviation 0.31 C, maximum 0.48 C, all 8 points within 2σ_meas. Spatial hot-spot location reproduced within 6 mm. IR thermogram vs CFD surface contour comparison documented. Monte Carlo 95% prediction intervals with model discrepancy added confirm all scenarios below safety thresholds with margin (ΔTout 95% upper bound 1.35 C vs 2.0 C criterion; surface temp ≤40.8 C vs 41 C criterion). Consistent underprediction at lowest flow (2 L/min) identified and noted as a scope limitation.</t>
+          <t>Outlet ΔT: mean absolute deviation 0.08 C, maximum 0.19 C across 8 points; 7/8 within 1σ_meas, 1/8 at 1.6σ_meas. Peak surface temperature: mean absolute deviation 0.31 C, maximum 0.48 C; all 8 points within 2σ_meas. Spatial hot-spot location reproduced within 6 mm from IR thermography. IR contours vs CFD surface temperature compared qualitatively (figs/ir_vs_cfd/). Model discrepancy characterized as Gaussian with σ = RMSE and incorporated into Monte Carlo UQ for conservative bound reporting. Meets stated target of ≤0.2 C mean bias and ≤0.3 C 95% limit for ΔTout.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3140,12 +3104,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly measure the stated safety concerns and are measurable both computationally and experimentally</t>
+          <t>QoIs directly measure the safety concerns (hemolysis risk from blood heating, tissue burn from surface temperature); measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Primary QoIs — bulk outlet blood temperature rise and peak housing surface temperature — directly map to the two stated safety concerns (hemolysis/thrombus risk via blood heating and tissue burn risk via surface temperature). Both are measurable computationally (mass-averaged and surface-averaged CFD outputs) and experimentally (fiber optic probes and IR/PT100 sensors). Secondary QoIs (heat split to blood, peak wetted-wall temperature) support mechanistic understanding. The Sobol analysis confirms these outputs are sensitive to the physical drivers (flow rate, motor loss) consistent with expected physics. Limitation noted that hemolysis and protein denaturation are not directly modeled; temperature is used as an accepted proxy metric.</t>
+          <t>Two primary QoIs directly address the stated safety concerns: (1) bulk outlet blood temperature rise (ΔTout) as proxy for blood thermal damage and hemolysis risk with established clinical threshold of 2.0 C; (2) peak housing exterior surface temperature as indicator of tissue burn risk with threshold 41 C. Both are computable from the CFD model and measurable in bench tests. Secondary QoI (heat split to blood) provides mechanistic understanding. Sensitivity analysis confirms flow rate and motor loss are dominant drivers, consistent with clinical risk factors. Limitation noted: no direct hemolysis or protein denaturation model coupled — temperature is an accepted proxy metric.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3169,16 +3133,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions span the intended operating envelope; non-dimensional similarity maintained; geometry is production-representative</t>
+          <t>Validation conditions span the full intended operating envelope; geometry and physics regime representative of in vivo use; gaps identified and bounded</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation spans the full intended operating envelope: 2–6 L/min and 2.6–3.4 W motor loss at 7,000–9,000 rpm (8 points). Test article is production-equivalent (SN M-THERM-017, final design Rev D). Saddle geometry, surface finish, and grease controlled to implant work instruction (WI-THERM-07). Blood analog viscosity matched to target shear rates; Re within 10%, Pr within 3.4% of blood. Heat generation distributed per actual winding layout. Gaps acknowledged: validation does not extend below 2 L/min (additional study planned for 1.5 L/min); air-side external handling conditions covered by separate tests; tissue conduction outside saddle covered by separate FEM. Device geometry changes &gt;0.2 mm wall thickness or potting substitution would require revalidation per stated scope boundaries.</t>
+          <t>Validation covers 2–6 L/min and 7,000–9,000 rpm with 8 operating points spanning the declared envelope, including boundary conditions (2.6–3.4 W motor loss). Production-equivalent geometry (Rev D) and controlled assembly per WI-THERM-07 used. Non-dimensional groups (Re within 10%, Pr within 3%) matched to in vivo conditions using viscosity-tuned analog. Gaps explicitly identified: (1) low-flow regime &lt;2 L/min not validated with slight underprediction tendency noted at 2 L/min; (2) in vivo external tissue conduction not modeled (separate FEM analysis referenced but not detailed here); (3) single device unit tested limits manufacturing variability assessment; (4) 6,000 rpm lower bound of rpm envelope has limited direct coverage in the 8-point matrix. Extrapolation below 2 L/min explicitly cautioned against.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3267,7 +3231,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The LVAD CHT model meets all stated performance requirements for thermal safety within the 2–6 L/min, 6,000–9,000 rpm, 2.6–3.4 W operating envelope. All 8 validation points show agreement within measurement uncertainty for outlet ΔTout (max deviation 0.19 C vs 0.3 C 95% limit requirement) and housing surface temperature (all within 2σ_meas). Monte Carlo 95% prediction bounds, including numerical, input, and model-discrepancy contributions, remain below both safety thresholds with clear margin (ΔTout ≤1.35 C vs 2.0 C limit; surface temp ≤40.8 C vs 41 C limit). Numerical quality is high (GCI95 ≤0.04 C; energy balance within 0.3%; residuals below prescribed targets). Code verification, independent peer review (IRR-CHT-2026-04 and external SME), and comprehensive UQ satisfy MRL 4 / High assurance requirements. Acceptance is conditioned on: (1) operating envelope restricted to 2–6 L/min and 6,000–9,000 rpm; (2) assembly per WI-THERM-07 enforced to maintain contact conductance assumption; (3) geometry restricted to final design Rev D (changes &gt;0.2 mm wall thickness or potting substitution require revalidation); (4) additional validation at 1.5 L/min to be completed before claims are extended below 2 L/min.</t>
+          <t>The LVAD motor conjugate heat transfer model demonstrates high credibility for its intended use. All safety thresholds are met with substantial margin: the 95% upper bound on blood temperature rise at the highest-risk condition (2 L/min, 3.4 W) is 1.35 C against a 2.0 C limit, and peak housing surface temperature 95% bounds remain ≤40.8 C against the 41 C limit. Numerical errors are negligible relative to decision thresholds (GCI95 ≤0.04 C). Model-to-test agreement meets stated performance targets (mean bias 0.08 C vs ≤0.2 C requirement). Comprehensive UQ propagates all major input, numerical, and model-form uncertainties. Independent internal and external peer review completed. Acceptance is conditioned on: (1) use remaining within the declared operating envelope (2–6 L/min, 6,000–9,000 rpm, 2.6–3.4 W); (2) mandatory adherence to assembly work instruction WI-THERM-07 for saddle mount contact; (3) additional validation at 1.5 L/min before extending applicability below 2 L/min; (4) revalidation required for housing wall thickness changes &gt;0.2 mm or potting material substitution.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
